--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_231_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_231_R24.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8292</v>
+        <v>3.2243</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0474</v>
+        <v>2.4511</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7818</v>
+        <v>0.7731</v>
       </c>
       <c r="G2" t="n">
-        <v>0.308</v>
+        <v>2.4052</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5955</v>
+        <v>2.4754</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9034</v>
+        <v>-0.0702</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4481</v>
+        <v>3.5813</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1947</v>
+        <v>3.277</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6428</v>
+        <v>0.3044</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1401</v>
+        <v>-1.1761</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4008</v>
+        <v>-0.8016</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.3746</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.232</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2713</v>
+        <v>0.1259</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1687</v>
+        <v>-0.1096</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>0.2355</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1418</v>
+        <v>-0.9304</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X2" t="n">
         <v>-0.1418</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.772</v>
+        <v>2.3736</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9483</v>
+        <v>1.1968</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1763</v>
+        <v>1.1768</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6967</v>
+        <v>0.308</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1345</v>
+        <v>-0.5955</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5622</v>
+        <v>0.9034</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8613</v>
+        <v>1.4481</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7141</v>
+        <v>-0.1947</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1472</v>
+        <v>1.6428</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1646</v>
+        <v>-1.1401</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5796</v>
+        <v>-0.4008</v>
       </c>
       <c r="O3" t="n">
-        <v>0.415</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P3" t="n">
+        <v>1.3917</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.3917</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9465</v>
+        <v>0.8158</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4787</v>
+        <v>-0.0193</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4679</v>
+        <v>0.8351</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6393</v>
+        <v>-0.1418</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6393</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7296</v>
+        <v>1.8155</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0908</v>
+        <v>1.5639</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6387</v>
+        <v>0.2516</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4052</v>
+        <v>1.7291</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4754</v>
+        <v>1.1703</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0702</v>
+        <v>0.5587</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5813</v>
+        <v>2.5837</v>
       </c>
       <c r="K4" t="n">
-        <v>3.277</v>
+        <v>2.3898</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3044</v>
+        <v>0.1939</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1761</v>
+        <v>-0.8547</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8016</v>
+        <v>-1.2195</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3746</v>
+        <v>0.3648</v>
       </c>
       <c r="P4" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.6237</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.8556</v>
-      </c>
       <c r="S4" t="n">
-        <v>-1.3689</v>
+        <v>-0.9651</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4699</v>
+        <v>-0.5895</v>
       </c>
       <c r="U4" t="n">
-        <v>0.101</v>
+        <v>-0.3756</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9304</v>
+        <v>0.8197</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7886</v>
+        <v>0.9615</v>
       </c>
       <c r="X4" t="n">
         <v>-0.1418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5392</v>
+        <v>0.3886</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4893</v>
+        <v>0.8002</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0499</v>
+        <v>-0.4115</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7291</v>
+        <v>1.6967</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1703</v>
+        <v>1.1345</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5587</v>
+        <v>0.5622</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5837</v>
+        <v>1.8613</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3898</v>
+        <v>1.7141</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1939</v>
+        <v>0.1472</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8547</v>
+        <v>-0.1646</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2195</v>
+        <v>-0.5796</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3648</v>
+        <v>0.415</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2415</v>
+        <v>0.5632</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6642</v>
+        <v>0.3306</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5772</v>
+        <v>0.2326</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8197</v>
+        <v>-1.6393</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9615</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.6393</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2383</v>
+        <v>-0.5094</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1136</v>
+        <v>0.145</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3519</v>
+        <v>-0.6544</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4976</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4037</v>
+        <v>0.1327</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2715</v>
+        <v>0.3029</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1322</v>
+        <v>-0.1702</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8511</v>
+        <v>-0.7502</v>
       </c>
       <c r="E7" t="n">
         <v>-0.5415</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3095</v>
+        <v>-0.2087</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8515</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4635</v>
+        <v>-0.3626</v>
       </c>
       <c r="T7" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0154</v>
+        <v>0.0854</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9203</v>
+        <v>-1.2375</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4015</v>
+        <v>-2.8305</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4812</v>
+        <v>1.5929</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6597</v>
+        <v>-2.1449</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.9437</v>
+        <v>-1.6998</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.716</v>
+        <v>-0.4451</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.3204</v>
+        <v>-3.0098</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.394</v>
+        <v>-1.9389</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0736</v>
+        <v>-1.0709</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3394</v>
+        <v>0.8649</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4502</v>
+        <v>0.2391</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7896</v>
+        <v>0.6258</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>1.791</v>
+        <v>0.1573</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9189</v>
+        <v>0.2126</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1278</v>
+        <v>-0.0553</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2525</v>
+        <v>1.214</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2525</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.596</v>
+        <v>-1.7824</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0545</v>
+        <v>-2.4317</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4585</v>
+        <v>0.6492</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1449</v>
+        <v>-3.6597</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6998</v>
+        <v>-2.9437</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4451</v>
+        <v>-0.716</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.0098</v>
+        <v>-3.3204</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9389</v>
+        <v>-3.394</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0709</v>
+        <v>0.0736</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8649</v>
+        <v>-0.3394</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2391</v>
+        <v>0.4502</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6258</v>
+        <v>-0.7896</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2012</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0114</v>
+        <v>0.8887</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1898</v>
+        <v>0.0402</v>
       </c>
       <c r="V9" t="n">
-        <v>1.214</v>
+        <v>0.2525</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2483</v>
+        <v>-1.8829</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.823</v>
+        <v>-1.6777</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4253</v>
+        <v>-0.2051</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-4.4696</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7946</v>
+        <v>-4.8141</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0401</v>
+        <v>0.3446</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3645</v>
+        <v>-3.7585</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0672</v>
+        <v>-4.8959</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4317</v>
+        <v>1.1374</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.39</v>
+        <v>-0.7111</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8618</v>
+        <v>0.0818</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4718</v>
+        <v>-0.7929</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4938</v>
+        <v>0.4217</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>0.2559</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.195</v>
+        <v>0.1658</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>2.3969</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4709</v>
+        <v>-3.1811</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9633</v>
+        <v>-1.823</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-1.3581</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4696</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.8141</v>
+        <v>-0.7946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3446</v>
+        <v>0.0401</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7585</v>
+        <v>-0.3645</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.8959</v>
+        <v>0.0672</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1374</v>
+        <v>-0.4317</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7111</v>
+        <v>-0.39</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0818</v>
+        <v>-0.8618</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7929</v>
+        <v>0.4718</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1663</v>
+        <v>-0.4266</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0297</v>
+        <v>-0.2987</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1366</v>
+        <v>-0.1278</v>
       </c>
       <c r="V11" t="n">
-        <v>2.3969</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8197</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7698</v>
+        <v>-4.1897</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7092</v>
+        <v>-3.1627</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0606</v>
+        <v>-1.027</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2511</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3589</v>
+        <v>0.2212</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.224</v>
+        <v>0.3224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.224699999999999</v>
+        <v>-5.7312</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.803599999999999</v>
+        <v>-6.310099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5789</v>
+        <v>0.5787999999999998</v>
       </c>
       <c r="G13" t="n">
         <v>-9.4899</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.917300000000001</v>
+        <v>-7.9173</v>
       </c>
       <c r="I13" t="n">
         <v>-1.5727</v>
@@ -1450,10 +1450,10 @@
         <v>-0.4862000000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.9347</v>
+        <v>-5.934699999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.848199999999999</v>
+        <v>-4.8482</v>
       </c>
       <c r="O13" t="n">
         <v>-1.0866</v>
@@ -1462,19 +1462,19 @@
         <v>2.319499999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.2782</v>
+        <v>-9.278200000000002</v>
       </c>
       <c r="R13" t="n">
         <v>11.5978</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1183999999999996</v>
+        <v>1.6124</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6456000000000002</v>
+        <v>0.8479000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7643999999999995</v>
+        <v>0.7644</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1728000000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4133</v>
+        <v>3.3299</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0061</v>
+        <v>2.4261</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4072</v>
+        <v>0.9038</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1499</v>
+        <v>5.3053</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4309</v>
+        <v>2.2103</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.281</v>
+        <v>3.095</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9008</v>
+        <v>4.0258</v>
       </c>
       <c r="K14" t="n">
-        <v>0.864</v>
+        <v>0.9243</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0368</v>
+        <v>3.1015</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7509</v>
+        <v>1.2795</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4331</v>
+        <v>1.2861</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3178</v>
+        <v>-0.0065</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>3.333</v>
+        <v>-0.063</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1928</v>
+        <v>-0.44</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1401</v>
+        <v>0.3769</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9304</v>
+        <v>-2.1444</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2683</v>
+        <v>2.7742</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8363</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.432</v>
+        <v>1.8725</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3053</v>
+        <v>2.349</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2103</v>
+        <v>0.9303</v>
       </c>
       <c r="I15" t="n">
-        <v>3.095</v>
+        <v>1.4187</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0258</v>
+        <v>2.1986</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9243</v>
+        <v>0.0406</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1015</v>
+        <v>2.1581</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2795</v>
+        <v>0.1503</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2861</v>
+        <v>0.8897</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0065</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1246</v>
+        <v>0.1907</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0297</v>
+        <v>-0.279</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0949</v>
+        <v>0.4696</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1444</v>
+        <v>0.9304</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8877</v>
+        <v>2.4024</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6657999999999999</v>
+        <v>1.6471</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2219</v>
+        <v>0.7553</v>
       </c>
       <c r="G16" t="n">
-        <v>2.349</v>
+        <v>0.1499</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9303</v>
+        <v>0.4309</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4187</v>
+        <v>-0.281</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1986</v>
+        <v>0.9008</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0406</v>
+        <v>0.864</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1581</v>
+        <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1503</v>
+        <v>-0.7509</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8897</v>
+        <v>-0.4331</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.3178</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6959</v>
+        <v>1.3221</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5149</v>
+        <v>0.8338</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.181</v>
+        <v>0.4883</v>
       </c>
       <c r="V16" t="n">
         <v>0.9304</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7886</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.754</v>
+        <v>2.3051</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.858</v>
+        <v>-0.3862</v>
       </c>
       <c r="F17" t="n">
-        <v>2.612</v>
+        <v>2.6913</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7067</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1296</v>
+        <v>0.4215</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.963</v>
+        <v>-0.4911</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8334</v>
+        <v>0.9127</v>
       </c>
       <c r="V17" t="n">
         <v>2.8223</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5984</v>
+        <v>2.1096</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7543</v>
+        <v>1.1082</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8441</v>
+        <v>1.0014</v>
       </c>
       <c r="G18" t="n">
         <v>0.3693</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6291</v>
+        <v>-0.118</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2908</v>
+        <v>0.063</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3383</v>
+        <v>-0.181</v>
       </c>
       <c r="V18" t="n">
         <v>0.9304</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4523</v>
+        <v>0.8068</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9041</v>
+        <v>-1.3144</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3564</v>
+        <v>2.1212</v>
       </c>
       <c r="G19" t="n">
         <v>0.9192</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2675</v>
+        <v>0.6221</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5149</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7824</v>
+        <v>0.5472</v>
       </c>
       <c r="V19" t="n">
         <v>0.4254</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3341</v>
+        <v>-0.2038</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7623</v>
+        <v>-0.7774</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4282</v>
+        <v>0.5736</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1082</v>
+        <v>-0.1965</v>
       </c>
       <c r="H20" t="n">
-        <v>1.353</v>
+        <v>0.3589</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2447</v>
+        <v>-0.5555</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5674</v>
+        <v>-0.5357</v>
       </c>
       <c r="K20" t="n">
-        <v>0.306</v>
+        <v>0.6456</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8734</v>
+        <v>-1.1813</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6757</v>
+        <v>0.3392</v>
       </c>
       <c r="N20" t="n">
-        <v>1.047</v>
+        <v>-0.2866</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3713</v>
+        <v>0.6258</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0215</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0351</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U20" t="n">
         <v>0.0567</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0409</v>
+        <v>-0.5415</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3671</v>
+        <v>-2.1162</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3262</v>
+        <v>1.5747</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1965</v>
+        <v>0.1082</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3589</v>
+        <v>1.353</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5555</v>
+        <v>-1.2447</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5357</v>
+        <v>-0.5674</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6456</v>
+        <v>0.306</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1813</v>
+        <v>-0.8734</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3392</v>
+        <v>0.6757</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2866</v>
+        <v>1.047</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6258</v>
+        <v>-0.3713</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.847</v>
+        <v>-0.1858</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6563</v>
+        <v>-0.389</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1906</v>
+        <v>0.2032</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.515</v>
+        <v>-1.1783</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1064</v>
+        <v>0.1295</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4086</v>
+        <v>-1.3078</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6081</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1568</v>
+        <v>0.1799</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V22" t="n">
         <v>-1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2592</v>
+        <v>-2.2206</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8435</v>
+        <v>-2.1974</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4157</v>
+        <v>-0.0232</v>
       </c>
       <c r="G23" t="n">
         <v>1.8005</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1577</v>
+        <v>-0.119</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2715</v>
+        <v>-0.0824</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4292</v>
+        <v>-0.0367</v>
       </c>
       <c r="V23" t="n">
         <v>-3.4381</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.224799999999998</v>
+        <v>9.583799999999997</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5788999999999995</v>
+        <v>-0.5790000000000008</v>
       </c>
       <c r="F24" t="n">
-        <v>7.8037</v>
+        <v>10.1628</v>
       </c>
       <c r="G24" t="n">
         <v>9.4901</v>
@@ -2314,7 +2314,7 @@
         <v>3.0695</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4861999999999998</v>
+        <v>0.4862</v>
       </c>
       <c r="P24" t="n">
         <v>-2.3196</v>
@@ -2326,13 +2326,13 @@
         <v>9.278200000000002</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1186999999999998</v>
+        <v>2.2406</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7644</v>
+        <v>-0.7645000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6457999999999999</v>
+        <v>3.0049</v>
       </c>
       <c r="V24" t="n">
         <v>0.1727999999999996</v>
